--- a/exploratory_data_analisys/normalization/risultati/correlazioni_dispersioni/matrice_correlazione.xlsx
+++ b/exploratory_data_analisys/normalization/risultati/correlazioni_dispersioni/matrice_correlazione.xlsx
@@ -425,76 +425,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>IslandArea</t>
+          <t>Densità_pop</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Densità_pop</t>
+          <t>evi</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>evi</t>
+          <t>eolico</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>eolico</t>
+          <t>eolico_std</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>eolico_std</t>
+          <t>offshore</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>offshore</t>
+          <t>gdp_pro_capite</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>gdp_pro_capite</t>
+          <t>geothermal_potential</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>geothermal_potential</t>
+          <t>hydro</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>hydro</t>
+          <t>temp</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>temp</t>
+          <t>solar_pow</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>solar_pow</t>
+          <t>solar_seas_ind</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>solar_seas_ind</t>
+          <t>superficie_res</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>superficie_res</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>gdp_pop_urban_merged</t>
         </is>
@@ -503,686 +498,598 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IslandArea</t>
+          <t>Densità_pop</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3948814216348746</v>
+        <v>-0.1603397212416324</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3590493258494196</v>
+        <v>0.009330998897721515</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.002606272864746878</v>
+        <v>0.02880576730824429</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0338163586333563</v>
+        <v>-0.1143036260706121</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1597983747142711</v>
+        <v>-0.01286722699427263</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.01656613162897247</v>
+        <v>-0.07275041177163549</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2532036142969715</v>
+        <v>-0.2785877550604335</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5184953941987716</v>
+        <v>0.1314864967720103</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.02188452262088182</v>
+        <v>0.1205675323282588</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.04539422401216146</v>
+        <v>-0.1441789757391418</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007017873778052247</v>
+        <v>-0.2629753934025799</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.147948871827847</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.5644457106402099</v>
+        <v>0.4305323245044078</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Densità_pop</t>
+          <t>evi</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.3948814216348746</v>
+        <v>-0.1603397212416324</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1603397212416324</v>
+        <v>-0.07900743900357796</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009330998897721517</v>
+        <v>0.1102022605438193</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02880576730824429</v>
+        <v>-0.2353967482676732</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1143036260706121</v>
+        <v>-0.3797259900774364</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.01286722699427264</v>
+        <v>0.01631506471910429</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07275041177163549</v>
+        <v>0.2261718998919184</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2785877550604335</v>
+        <v>0.3540270520001519</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1314864967720103</v>
+        <v>-0.01352937325599862</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1205675323282588</v>
+        <v>-0.272643510846157</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1441789757391418</v>
+        <v>0.201205355571463</v>
       </c>
       <c r="N3" t="n">
-        <v>0.06596117087614567</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.4305323245043788</v>
+        <v>0.1299100623289071</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>evi</t>
+          <t>eolico</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3590493258494196</v>
+        <v>0.009330998897721515</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1603397212416324</v>
+        <v>-0.07900743900357796</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.07900743900357796</v>
+        <v>-0.4432968578586725</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1102022605438193</v>
+        <v>0.5343062955085277</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2353967482676732</v>
+        <v>0.2951591049250742</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3797259900774364</v>
+        <v>0.04009085647849257</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01631506471910429</v>
+        <v>-0.315266892804187</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2261718998919184</v>
+        <v>-0.3348280940248978</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3540270520001519</v>
+        <v>-0.1415374667843115</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.01352937325599862</v>
+        <v>0.291179712668002</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.272643510846157</v>
+        <v>0.0853060141049871</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2163144824324935</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.1299100623289144</v>
+        <v>0.03682966666958746</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>eolico</t>
+          <t>eolico_std</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.002606272864746878</v>
+        <v>0.02880576730824429</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009330998897721517</v>
+        <v>0.1102022605438193</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07900743900357796</v>
+        <v>-0.4432968578586725</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4432968578586725</v>
+        <v>-0.4860121171606608</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5343062955085277</v>
+        <v>-0.395941560555787</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2951591049250742</v>
+        <v>-0.05800802865680036</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04009085647849257</v>
+        <v>0.1896766178681986</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.315266892804187</v>
+        <v>0.405756542317018</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3348280940248978</v>
+        <v>0.1299171412307012</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1415374667843115</v>
+        <v>-0.1993535074029822</v>
       </c>
       <c r="M5" t="n">
-        <v>0.291179712668002</v>
+        <v>-0.06874434558699304</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1286920967078817</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.03682966666957034</v>
+        <v>-0.05805135624652791</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>eolico_std</t>
+          <t>offshore</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0338163586333563</v>
+        <v>-0.1143036260706121</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02880576730824429</v>
+        <v>-0.2353967482676732</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1102022605438193</v>
+        <v>0.5343062955085277</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4432968578586725</v>
+        <v>-0.4860121171606608</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4860121171606608</v>
+        <v>0.526716413984201</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.395941560555787</v>
+        <v>0.1813550853116642</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05800802865680036</v>
+        <v>-0.03545068496768165</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1896766178681986</v>
+        <v>-0.628808751914488</v>
       </c>
       <c r="K6" t="n">
-        <v>0.405756542317018</v>
+        <v>-0.3352777296516733</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1299171412307012</v>
+        <v>0.4306311454102212</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1993535074029822</v>
+        <v>0.1490077093348467</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0856396850143679</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-0.05805135624652167</v>
+        <v>0.1195719517636516</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>offshore</t>
+          <t>gdp_pro_capite</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1597983747142711</v>
+        <v>-0.01286722699427263</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1143036260706121</v>
+        <v>-0.3797259900774364</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2353967482676732</v>
+        <v>0.2951591049250742</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5343062955085277</v>
+        <v>-0.395941560555787</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4860121171606608</v>
+        <v>0.526716413984201</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.526716413984201</v>
+        <v>0.1113036205754714</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1813550853116642</v>
+        <v>-0.08848663028900723</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.03545068496768164</v>
+        <v>-0.6657458635541963</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.628808751914488</v>
+        <v>-0.3863401456911399</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3352777296516733</v>
+        <v>0.476892939328316</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4306311454102212</v>
+        <v>0.01983470113626488</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04061070470607144</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.1195719517636486</v>
+        <v>0.09396370877623202</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>gdp_pro_capite</t>
+          <t>geothermal_potential</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01656613162897247</v>
+        <v>-0.07275041177163549</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.01286722699427264</v>
+        <v>0.01631506471910429</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3797259900774364</v>
+        <v>0.04009085647849257</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2951591049250742</v>
+        <v>-0.05800802865680036</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.395941560555787</v>
+        <v>0.1813550853116642</v>
       </c>
       <c r="G8" t="n">
-        <v>0.526716413984201</v>
+        <v>0.1113036205754714</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1113036205754714</v>
+        <v>0.07879283758933926</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.08848663028900723</v>
+        <v>-0.1202594386102731</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6657458635541963</v>
+        <v>-0.0203210309605735</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3863401456911399</v>
+        <v>0.01644984874082214</v>
       </c>
       <c r="M8" t="n">
-        <v>0.476892939328316</v>
+        <v>0.1617368246678593</v>
       </c>
       <c r="N8" t="n">
-        <v>0.05513694058092578</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.09396370877621529</v>
+        <v>0.1733027497441144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>geothermal_potential</t>
+          <t>hydro</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2532036142969715</v>
+        <v>-0.2785877550604335</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.07275041177163549</v>
+        <v>0.2261718998919184</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01631506471910429</v>
+        <v>-0.315266892804187</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04009085647849257</v>
+        <v>0.1896766178681986</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.05800802865680036</v>
+        <v>-0.03545068496768165</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1813550853116642</v>
+        <v>-0.08848663028900723</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1113036205754714</v>
+        <v>0.07879283758933926</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.07879283758933926</v>
+        <v>-0.003814604228985273</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1202594386102731</v>
+        <v>-0.1235031640064981</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0203210309605735</v>
+        <v>0.06428938629553267</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01644984874082214</v>
+        <v>0.3608168886284009</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.04390667359678476</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.1733027497441182</v>
+        <v>0.2384061012346925</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hydro</t>
+          <t>temp</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5184953941987716</v>
+        <v>0.1314864967720103</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.2785877550604335</v>
+        <v>0.3540270520001519</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2261718998919184</v>
+        <v>-0.3348280940248978</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.315266892804187</v>
+        <v>0.405756542317018</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1896766178681986</v>
+        <v>-0.628808751914488</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.03545068496768164</v>
+        <v>-0.6657458635541963</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.08848663028900723</v>
+        <v>-0.1202594386102731</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07879283758933926</v>
+        <v>-0.003814604228985273</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.003814604228985273</v>
+        <v>0.6679941812612133</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1235031640064981</v>
+        <v>-0.7787456902517266</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06428938629553269</v>
+        <v>0.004925822020497769</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1274455383723407</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.2384061012347072</v>
+        <v>0.01190654275210732</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>temp</t>
+          <t>solar_pow</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.02188452262088182</v>
+        <v>0.1205675323282588</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1314864967720103</v>
+        <v>-0.01352937325599862</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3540270520001519</v>
+        <v>-0.1415374667843115</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3348280940248978</v>
+        <v>0.1299171412307012</v>
       </c>
       <c r="F11" t="n">
-        <v>0.405756542317018</v>
+        <v>-0.3352777296516733</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.628808751914488</v>
+        <v>-0.3863401456911399</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6657458635541963</v>
+        <v>-0.0203210309605735</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1202594386102731</v>
+        <v>-0.1235031640064981</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.003814604228985273</v>
+        <v>0.6679941812612133</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6679941812612133</v>
+        <v>-0.7279444287650078</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7787456902517266</v>
+        <v>0.0405949150473817</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01960986702368931</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.01190654275212105</v>
+        <v>0.002444444652593677</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>solar_pow</t>
+          <t>solar_seas_ind</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.04539422401216146</v>
+        <v>-0.1441789757391418</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1205675323282588</v>
+        <v>-0.272643510846157</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.01352937325599862</v>
+        <v>0.291179712668002</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1415374667843115</v>
+        <v>-0.1993535074029822</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1299171412307012</v>
+        <v>0.4306311454102212</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3352777296516733</v>
+        <v>0.476892939328316</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3863401456911399</v>
+        <v>0.01644984874082214</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0203210309605735</v>
+        <v>0.06428938629553267</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1235031640064981</v>
+        <v>-0.7787456902517266</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6679941812612133</v>
+        <v>-0.7279444287650078</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7279444287650078</v>
+        <v>-0.007746067160362753</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1265143597509152</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.002444444652602398</v>
+        <v>-0.0482606182313349</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>solar_seas_ind</t>
+          <t>superficie_res</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.007017873778052247</v>
+        <v>-0.2629753934025799</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.1441789757391418</v>
+        <v>0.201205355571463</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.272643510846157</v>
+        <v>0.0853060141049871</v>
       </c>
       <c r="E13" t="n">
-        <v>0.291179712668002</v>
+        <v>-0.06874434558699304</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1993535074029822</v>
+        <v>0.1490077093348467</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4306311454102212</v>
+        <v>0.01983470113626488</v>
       </c>
       <c r="H13" t="n">
-        <v>0.476892939328316</v>
+        <v>0.1617368246678593</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01644984874082214</v>
+        <v>0.3608168886284009</v>
       </c>
       <c r="J13" t="n">
-        <v>0.06428938629553269</v>
+        <v>0.004925822020497769</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.7787456902517266</v>
+        <v>0.0405949150473817</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7279444287650078</v>
+        <v>-0.007746067160362753</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.00176666841636391</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-0.04826061823134397</v>
+        <v>0.465272961541745</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>superficie_res</t>
+          <t>gdp_pop_urban_merged</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.147948871827847</v>
+        <v>0.4305323245044078</v>
       </c>
       <c r="C14" t="n">
-        <v>0.06596117087614567</v>
+        <v>0.1299100623289071</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2163144824324935</v>
+        <v>0.03682966666958746</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1286920967078817</v>
+        <v>-0.05805135624652791</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0856396850143679</v>
+        <v>0.1195719517636516</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04061070470607144</v>
+        <v>0.09396370877623202</v>
       </c>
       <c r="H14" t="n">
-        <v>0.05513694058092578</v>
+        <v>0.1733027497441144</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.04390667359678476</v>
+        <v>0.2384061012346925</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1274455383723407</v>
+        <v>0.01190654275210732</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01960986702368931</v>
+        <v>0.002444444652593677</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1265143597509152</v>
+        <v>-0.0482606182313349</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.00176666841636391</v>
+        <v>0.465272961541745</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-0.06496464256838543</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>gdp_pop_urban_merged</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.5644457106402099</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.4305323245043788</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.1299100623289144</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.03682966666957034</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.05805135624652167</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.1195719517636486</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.09396370877621529</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.1733027497441182</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.2384061012347072</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.01190654275212105</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.002444444652602398</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-0.04826061823134397</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-0.06496464256838543</v>
-      </c>
-      <c r="O15" t="n">
         <v>1</v>
       </c>
     </row>
